--- a/backend/data/financials_by_company/0915.HK.xlsx
+++ b/backend/data/financials_by_company/0915.HK.xlsx
@@ -657,55 +657,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>67.11173599999999</v>
+        <v>9113.136095</v>
       </c>
       <c r="C2" t="n">
-        <v>0.067112</v>
+        <v>0.032899</v>
       </c>
       <c r="D2" t="n">
-        <v>3856000</v>
+        <v>5099000</v>
       </c>
       <c r="E2" t="n">
-        <v>1000</v>
+        <v>277000</v>
       </c>
       <c r="F2" t="n">
-        <v>1000</v>
+        <v>277000</v>
       </c>
       <c r="G2" t="n">
-        <v>2655000</v>
+        <v>4086000</v>
       </c>
       <c r="H2" t="n">
-        <v>959000</v>
+        <v>1049000</v>
       </c>
       <c r="I2" t="n">
-        <v>24278000</v>
+        <v>41727000</v>
       </c>
       <c r="J2" t="n">
-        <v>3857000</v>
+        <v>5376000</v>
       </c>
       <c r="K2" t="n">
-        <v>2898000</v>
+        <v>4327000</v>
       </c>
       <c r="L2" t="n">
-        <v>315000</v>
+        <v>54000</v>
       </c>
       <c r="M2" t="n">
-        <v>52000</v>
+        <v>102000</v>
       </c>
       <c r="N2" t="n">
-        <v>367000</v>
+        <v>161000</v>
       </c>
       <c r="O2" t="n">
-        <v>2654067.111736</v>
+        <v>3818113.136095</v>
       </c>
       <c r="P2" t="n">
-        <v>2655000</v>
+        <v>4086000</v>
       </c>
       <c r="Q2" t="n">
-        <v>39271000</v>
+        <v>58745000</v>
       </c>
       <c r="R2" t="n">
         <v>1509593000</v>
@@ -714,137 +714,139 @@
         <v>1509593000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="V2" t="n">
-        <v>2655000</v>
+        <v>4086000</v>
       </c>
       <c r="W2" t="n">
-        <v>2655000</v>
+        <v>4086000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2655000</v>
+        <v>4086000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2655000</v>
+        <v>4086000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2655000</v>
+        <v>4086000</v>
       </c>
       <c r="AB2" t="n">
-        <v>191000</v>
+        <v>139000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2846000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>24000</v>
-      </c>
+        <v>4225000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>277000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>-277000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
       <c r="AH2" t="n">
-        <v>315000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>54000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>52000</v>
+        <v>102000</v>
       </c>
       <c r="AK2" t="n">
-        <v>367000</v>
+        <v>161000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2506000</v>
+        <v>3894000</v>
       </c>
       <c r="AM2" t="n">
-        <v>14993000</v>
+        <v>17018000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-136000</v>
+        <v>220000</v>
       </c>
       <c r="AO2" t="n">
-        <v>15440000</v>
+        <v>17392000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1712000</v>
+        <v>3133000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13728000</v>
+        <v>14259000</v>
       </c>
       <c r="AR2" t="n">
-        <v>17499000</v>
+        <v>20912000</v>
       </c>
       <c r="AS2" t="n">
-        <v>24278000</v>
+        <v>41727000</v>
       </c>
       <c r="AT2" t="n">
-        <v>41777000</v>
+        <v>62639000</v>
       </c>
       <c r="AU2" t="n">
-        <v>41777000</v>
+        <v>62639000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2371.124479</v>
+        <v>-92688.34258500001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08468299999999999</v>
+        <v>0.190325</v>
       </c>
       <c r="D3" t="n">
-        <v>3152000</v>
+        <v>2966000</v>
       </c>
       <c r="E3" t="n">
-        <v>28000</v>
+        <v>-487000</v>
       </c>
       <c r="F3" t="n">
-        <v>28000</v>
+        <v>-487000</v>
       </c>
       <c r="G3" t="n">
-        <v>1978000</v>
+        <v>1021000</v>
       </c>
       <c r="H3" t="n">
-        <v>907000</v>
+        <v>1119000</v>
       </c>
       <c r="I3" t="n">
-        <v>27302000</v>
+        <v>34776000</v>
       </c>
       <c r="J3" t="n">
-        <v>3180000</v>
+        <v>2479000</v>
       </c>
       <c r="K3" t="n">
-        <v>2273000</v>
+        <v>1360000</v>
       </c>
       <c r="L3" t="n">
-        <v>328000</v>
+        <v>136000</v>
       </c>
       <c r="M3" t="n">
-        <v>112000</v>
+        <v>99000</v>
       </c>
       <c r="N3" t="n">
-        <v>441000</v>
+        <v>240000</v>
       </c>
       <c r="O3" t="n">
-        <v>1952371.124479</v>
+        <v>1415311.657415</v>
       </c>
       <c r="P3" t="n">
-        <v>1978000</v>
+        <v>1021000</v>
       </c>
       <c r="Q3" t="n">
-        <v>42622000</v>
+        <v>50320000</v>
       </c>
       <c r="R3" t="n">
         <v>1509593000</v>
@@ -853,141 +855,139 @@
         <v>1509593000</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0013</v>
+        <v>0.0007</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0013</v>
+        <v>0.0007</v>
       </c>
       <c r="V3" t="n">
-        <v>1978000</v>
+        <v>1021000</v>
       </c>
       <c r="W3" t="n">
-        <v>1978000</v>
+        <v>1021000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1978000</v>
+        <v>1021000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1978000</v>
+        <v>1021000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1978000</v>
+        <v>1021000</v>
       </c>
       <c r="AB3" t="n">
-        <v>183000</v>
+        <v>240000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2161000</v>
+        <v>1261000</v>
       </c>
       <c r="AD3" t="n">
-        <v>72000</v>
+        <v>54000</v>
       </c>
       <c r="AE3" t="n">
-        <v>28000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-28000</v>
-      </c>
+        <v>-519000</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>519000</v>
       </c>
       <c r="AH3" t="n">
-        <v>328000</v>
+        <v>136000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>112000</v>
+        <v>99000</v>
       </c>
       <c r="AK3" t="n">
-        <v>441000</v>
+        <v>240000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1733000</v>
+        <v>1558000</v>
       </c>
       <c r="AM3" t="n">
-        <v>15320000</v>
+        <v>15544000</v>
       </c>
       <c r="AN3" t="n">
-        <v>24000</v>
+        <v>-373000</v>
       </c>
       <c r="AO3" t="n">
-        <v>15752000</v>
+        <v>16867000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2878000</v>
+        <v>2619000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12874000</v>
+        <v>14248000</v>
       </c>
       <c r="AR3" t="n">
-        <v>17053000</v>
+        <v>17102000</v>
       </c>
       <c r="AS3" t="n">
-        <v>27302000</v>
+        <v>34776000</v>
       </c>
       <c r="AT3" t="n">
-        <v>44355000</v>
+        <v>51878000</v>
       </c>
       <c r="AU3" t="n">
-        <v>44355000</v>
+        <v>51878000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-92688.34258500001</v>
+        <v>2371.124479</v>
       </c>
       <c r="C4" t="n">
-        <v>0.190325</v>
+        <v>0.08468299999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>2966000</v>
+        <v>3152000</v>
       </c>
       <c r="E4" t="n">
-        <v>-487000</v>
+        <v>28000</v>
       </c>
       <c r="F4" t="n">
-        <v>-487000</v>
+        <v>28000</v>
       </c>
       <c r="G4" t="n">
-        <v>1021000</v>
+        <v>1978000</v>
       </c>
       <c r="H4" t="n">
-        <v>1119000</v>
+        <v>907000</v>
       </c>
       <c r="I4" t="n">
-        <v>34776000</v>
+        <v>27302000</v>
       </c>
       <c r="J4" t="n">
-        <v>2479000</v>
+        <v>3180000</v>
       </c>
       <c r="K4" t="n">
-        <v>1360000</v>
+        <v>2273000</v>
       </c>
       <c r="L4" t="n">
-        <v>136000</v>
+        <v>328000</v>
       </c>
       <c r="M4" t="n">
-        <v>99000</v>
+        <v>112000</v>
       </c>
       <c r="N4" t="n">
-        <v>240000</v>
+        <v>441000</v>
       </c>
       <c r="O4" t="n">
-        <v>1415311.657415</v>
+        <v>1952371.124479</v>
       </c>
       <c r="P4" t="n">
-        <v>1021000</v>
+        <v>1978000</v>
       </c>
       <c r="Q4" t="n">
-        <v>50320000</v>
+        <v>42622000</v>
       </c>
       <c r="R4" t="n">
         <v>1509593000</v>
@@ -996,139 +996,141 @@
         <v>1509593000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007</v>
+        <v>0.0013</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007</v>
+        <v>0.0013</v>
       </c>
       <c r="V4" t="n">
-        <v>1021000</v>
+        <v>1978000</v>
       </c>
       <c r="W4" t="n">
-        <v>1021000</v>
+        <v>1978000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1021000</v>
+        <v>1978000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1021000</v>
+        <v>1978000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1021000</v>
+        <v>1978000</v>
       </c>
       <c r="AB4" t="n">
-        <v>240000</v>
+        <v>183000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1261000</v>
+        <v>2161000</v>
       </c>
       <c r="AD4" t="n">
-        <v>54000</v>
+        <v>72000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-519000</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>28000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-28000</v>
+      </c>
       <c r="AG4" t="n">
-        <v>519000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>136000</v>
+        <v>328000</v>
       </c>
       <c r="AI4" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99000</v>
+        <v>112000</v>
       </c>
       <c r="AK4" t="n">
-        <v>240000</v>
+        <v>441000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1558000</v>
+        <v>1733000</v>
       </c>
       <c r="AM4" t="n">
-        <v>15544000</v>
+        <v>15320000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-373000</v>
+        <v>24000</v>
       </c>
       <c r="AO4" t="n">
-        <v>16867000</v>
+        <v>15752000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2619000</v>
+        <v>2878000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14248000</v>
+        <v>12874000</v>
       </c>
       <c r="AR4" t="n">
-        <v>17102000</v>
+        <v>17053000</v>
       </c>
       <c r="AS4" t="n">
-        <v>34776000</v>
+        <v>27302000</v>
       </c>
       <c r="AT4" t="n">
-        <v>51878000</v>
+        <v>44355000</v>
       </c>
       <c r="AU4" t="n">
-        <v>51878000</v>
+        <v>44355000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>9113.136095</v>
+        <v>67.11173599999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.032899</v>
+        <v>0.067112</v>
       </c>
       <c r="D5" t="n">
-        <v>5099000</v>
+        <v>3856000</v>
       </c>
       <c r="E5" t="n">
-        <v>277000</v>
+        <v>1000</v>
       </c>
       <c r="F5" t="n">
-        <v>277000</v>
+        <v>1000</v>
       </c>
       <c r="G5" t="n">
-        <v>4086000</v>
+        <v>2655000</v>
       </c>
       <c r="H5" t="n">
-        <v>1049000</v>
+        <v>959000</v>
       </c>
       <c r="I5" t="n">
-        <v>41727000</v>
+        <v>24278000</v>
       </c>
       <c r="J5" t="n">
-        <v>5376000</v>
+        <v>3857000</v>
       </c>
       <c r="K5" t="n">
-        <v>4327000</v>
+        <v>2898000</v>
       </c>
       <c r="L5" t="n">
-        <v>54000</v>
+        <v>315000</v>
       </c>
       <c r="M5" t="n">
-        <v>102000</v>
+        <v>52000</v>
       </c>
       <c r="N5" t="n">
-        <v>161000</v>
+        <v>367000</v>
       </c>
       <c r="O5" t="n">
-        <v>3818113.136095</v>
+        <v>2654067.111736</v>
       </c>
       <c r="P5" t="n">
-        <v>4086000</v>
+        <v>2655000</v>
       </c>
       <c r="Q5" t="n">
-        <v>58745000</v>
+        <v>39271000</v>
       </c>
       <c r="R5" t="n">
         <v>1509593000</v>
@@ -1137,86 +1139,84 @@
         <v>1509593000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0027</v>
+        <v>0.0018</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0027</v>
+        <v>0.0018</v>
       </c>
       <c r="V5" t="n">
-        <v>4086000</v>
+        <v>2655000</v>
       </c>
       <c r="W5" t="n">
-        <v>4086000</v>
+        <v>2655000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>4086000</v>
+        <v>2655000</v>
       </c>
       <c r="Z5" t="n">
-        <v>4086000</v>
+        <v>2655000</v>
       </c>
       <c r="AA5" t="n">
-        <v>4086000</v>
+        <v>2655000</v>
       </c>
       <c r="AB5" t="n">
-        <v>139000</v>
+        <v>191000</v>
       </c>
       <c r="AC5" t="n">
-        <v>4225000</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>2846000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>24000</v>
+      </c>
       <c r="AE5" t="n">
-        <v>277000</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-277000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
+        <v>-1000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>54000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5000</v>
-      </c>
+        <v>315000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>102000</v>
+        <v>52000</v>
       </c>
       <c r="AK5" t="n">
-        <v>161000</v>
+        <v>367000</v>
       </c>
       <c r="AL5" t="n">
-        <v>3894000</v>
+        <v>2506000</v>
       </c>
       <c r="AM5" t="n">
-        <v>17018000</v>
+        <v>14993000</v>
       </c>
       <c r="AN5" t="n">
-        <v>220000</v>
+        <v>-136000</v>
       </c>
       <c r="AO5" t="n">
-        <v>17392000</v>
+        <v>15440000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3133000</v>
+        <v>1712000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14259000</v>
+        <v>13728000</v>
       </c>
       <c r="AR5" t="n">
-        <v>20912000</v>
+        <v>17499000</v>
       </c>
       <c r="AS5" t="n">
-        <v>41727000</v>
+        <v>24278000</v>
       </c>
       <c r="AT5" t="n">
-        <v>62639000</v>
+        <v>41777000</v>
       </c>
       <c r="AU5" t="n">
-        <v>62639000</v>
+        <v>41777000</v>
       </c>
     </row>
   </sheetData>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>1509592701</v>
@@ -1531,37 +1531,37 @@
         <v>1509592701</v>
       </c>
       <c r="D2" t="n">
-        <v>4571000</v>
+        <v>6364000</v>
       </c>
       <c r="E2" t="n">
-        <v>15922000</v>
+        <v>10959000</v>
       </c>
       <c r="F2" t="n">
-        <v>19778000</v>
+        <v>15976000</v>
       </c>
       <c r="G2" t="n">
-        <v>15050000</v>
+        <v>9999000</v>
       </c>
       <c r="H2" t="n">
-        <v>15922000</v>
+        <v>10959000</v>
       </c>
       <c r="I2" t="n">
-        <v>715000</v>
+        <v>1347000</v>
       </c>
       <c r="J2" t="n">
-        <v>15922000</v>
+        <v>10959000</v>
       </c>
       <c r="K2" t="n">
-        <v>15922000</v>
+        <v>10959000</v>
       </c>
       <c r="L2" t="n">
-        <v>15922000</v>
+        <v>10959000</v>
       </c>
       <c r="M2" t="n">
-        <v>15922000</v>
+        <v>10959000</v>
       </c>
       <c r="N2" t="n">
-        <v>-161760000</v>
+        <v>-167468000</v>
       </c>
       <c r="O2" t="n">
         <v>153457000</v>
@@ -1573,128 +1573,130 @@
         <v>20128000</v>
       </c>
       <c r="R2" t="n">
-        <v>14087000</v>
+        <v>19889000</v>
       </c>
       <c r="S2" t="n">
-        <v>488000</v>
+        <v>798000</v>
       </c>
       <c r="T2" t="n">
-        <v>175000</v>
+        <v>257000</v>
       </c>
       <c r="U2" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>139000</v>
+        <v>392000</v>
       </c>
       <c r="W2" t="n">
-        <v>139000</v>
+        <v>392000</v>
       </c>
       <c r="X2" t="n">
-        <v>154000</v>
+        <v>149000</v>
       </c>
       <c r="Y2" t="n">
-        <v>13599000</v>
+        <v>19091000</v>
       </c>
       <c r="Z2" t="n">
-        <v>4432000</v>
+        <v>5972000</v>
       </c>
       <c r="AA2" t="n">
-        <v>576000</v>
+        <v>955000</v>
       </c>
       <c r="AB2" t="n">
-        <v>3856000</v>
+        <v>5017000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-154000</v>
+        <v>-149000</v>
       </c>
       <c r="AD2" t="n">
-        <v>4271000</v>
+        <v>8568000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2299000</v>
+        <v>4010000</v>
       </c>
       <c r="AF2" t="n">
-        <v>523000</v>
+        <v>305000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1449000</v>
+        <v>4253000</v>
       </c>
       <c r="AH2" t="n">
-        <v>30009000</v>
+        <v>30848000</v>
       </c>
       <c r="AI2" t="n">
-        <v>1360000</v>
+        <v>1758000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>190000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>282000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
       <c r="AL2" t="n">
-        <v>95000</v>
+        <v>135000</v>
       </c>
       <c r="AM2" t="n">
-        <v>95000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>135000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
       <c r="AO2" t="n">
-        <v>1075000</v>
+        <v>1341000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-3493000</v>
+        <v>-3646000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4568000</v>
+        <v>4987000</v>
       </c>
       <c r="AR2" t="n">
-        <v>30000</v>
+        <v>1341000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2996000</v>
+        <v>3080000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1542000</v>
+        <v>1907000</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>28649000</v>
+        <v>29090000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1010000</v>
+        <v>1731000</v>
       </c>
       <c r="AX2" t="n">
-        <v>1725000</v>
+        <v>772000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1725000</v>
+        <v>772000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>959000</v>
+        <v>2477000</v>
       </c>
       <c r="BA2" t="n">
-        <v>3901000</v>
+        <v>8006000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-630000</v>
+        <v>-1175000</v>
       </c>
       <c r="BC2" t="n">
-        <v>4531000</v>
+        <v>9181000</v>
       </c>
       <c r="BD2" t="n">
-        <v>21054000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5700000</v>
-      </c>
+        <v>16104000</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
-        <v>15354000</v>
+        <v>16104000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1509592701</v>
@@ -1703,37 +1705,37 @@
         <v>1509592701</v>
       </c>
       <c r="D3" t="n">
-        <v>5709000</v>
+        <v>5672000</v>
       </c>
       <c r="E3" t="n">
-        <v>13329000</v>
+        <v>11260000</v>
       </c>
       <c r="F3" t="n">
-        <v>17481000</v>
+        <v>15532000</v>
       </c>
       <c r="G3" t="n">
-        <v>12129000</v>
+        <v>10679000</v>
       </c>
       <c r="H3" t="n">
-        <v>13329000</v>
+        <v>11260000</v>
       </c>
       <c r="I3" t="n">
-        <v>1557000</v>
+        <v>1400000</v>
       </c>
       <c r="J3" t="n">
-        <v>13329000</v>
+        <v>11260000</v>
       </c>
       <c r="K3" t="n">
-        <v>13329000</v>
+        <v>11260000</v>
       </c>
       <c r="L3" t="n">
-        <v>13329000</v>
+        <v>11260000</v>
       </c>
       <c r="M3" t="n">
-        <v>13329000</v>
+        <v>11260000</v>
       </c>
       <c r="N3" t="n">
-        <v>-164449000</v>
+        <v>-166423000</v>
       </c>
       <c r="O3" t="n">
         <v>153457000</v>
@@ -1745,128 +1747,122 @@
         <v>20128000</v>
       </c>
       <c r="R3" t="n">
-        <v>16087000</v>
+        <v>15013000</v>
       </c>
       <c r="S3" t="n">
-        <v>932000</v>
+        <v>877000</v>
       </c>
       <c r="T3" t="n">
-        <v>212000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
+        <v>174000</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>566000</v>
+        <v>703000</v>
       </c>
       <c r="W3" t="n">
-        <v>566000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>154000</v>
-      </c>
+        <v>703000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>15155000</v>
+        <v>14136000</v>
       </c>
       <c r="Z3" t="n">
-        <v>5143000</v>
+        <v>4969000</v>
       </c>
       <c r="AA3" t="n">
-        <v>991000</v>
+        <v>697000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4152000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-154000</v>
-      </c>
+        <v>4272000</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>1850000</v>
+        <v>4559000</v>
       </c>
       <c r="AE3" t="n">
-        <v>3397000</v>
+        <v>3228000</v>
       </c>
       <c r="AF3" t="n">
-        <v>348000</v>
+        <v>446000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1502000</v>
+        <v>885000</v>
       </c>
       <c r="AH3" t="n">
-        <v>29416000</v>
+        <v>26273000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2132000</v>
+        <v>1458000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>309000</v>
+        <v>221000</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>123000</v>
+        <v>167000</v>
       </c>
       <c r="AM3" t="n">
-        <v>123000</v>
+        <v>167000</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>1700000</v>
+        <v>1070000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-3409000</v>
+        <v>-3818000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5109000</v>
+        <v>4888000</v>
       </c>
       <c r="AR3" t="n">
-        <v>39000</v>
+        <v>1070000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2932000</v>
+        <v>3004000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2138000</v>
+        <v>1884000</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>27284000</v>
+        <v>24815000</v>
       </c>
       <c r="AW3" t="n">
-        <v>505000</v>
+        <v>728000</v>
       </c>
       <c r="AX3" t="n">
-        <v>861000</v>
+        <v>837000</v>
       </c>
       <c r="AY3" t="n">
-        <v>861000</v>
+        <v>837000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1847000</v>
+        <v>1834000</v>
       </c>
       <c r="BA3" t="n">
-        <v>3931000</v>
+        <v>3210000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-668000</v>
+        <v>-660000</v>
       </c>
       <c r="BC3" t="n">
-        <v>4599000</v>
+        <v>3870000</v>
       </c>
       <c r="BD3" t="n">
-        <v>20140000</v>
+        <v>18206000</v>
       </c>
       <c r="BE3" t="n">
-        <v>3538000</v>
+        <v>3724000</v>
       </c>
       <c r="BF3" t="n">
-        <v>16602000</v>
+        <v>14482000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1509592701</v>
@@ -1875,37 +1871,37 @@
         <v>1509592701</v>
       </c>
       <c r="D4" t="n">
-        <v>5672000</v>
+        <v>5709000</v>
       </c>
       <c r="E4" t="n">
-        <v>11260000</v>
+        <v>13329000</v>
       </c>
       <c r="F4" t="n">
-        <v>15532000</v>
+        <v>17481000</v>
       </c>
       <c r="G4" t="n">
-        <v>10679000</v>
+        <v>12129000</v>
       </c>
       <c r="H4" t="n">
-        <v>11260000</v>
+        <v>13329000</v>
       </c>
       <c r="I4" t="n">
-        <v>1400000</v>
+        <v>1557000</v>
       </c>
       <c r="J4" t="n">
-        <v>11260000</v>
+        <v>13329000</v>
       </c>
       <c r="K4" t="n">
-        <v>11260000</v>
+        <v>13329000</v>
       </c>
       <c r="L4" t="n">
-        <v>11260000</v>
+        <v>13329000</v>
       </c>
       <c r="M4" t="n">
-        <v>11260000</v>
+        <v>13329000</v>
       </c>
       <c r="N4" t="n">
-        <v>-166423000</v>
+        <v>-164449000</v>
       </c>
       <c r="O4" t="n">
         <v>153457000</v>
@@ -1917,122 +1913,128 @@
         <v>20128000</v>
       </c>
       <c r="R4" t="n">
-        <v>15013000</v>
+        <v>16087000</v>
       </c>
       <c r="S4" t="n">
-        <v>877000</v>
+        <v>932000</v>
       </c>
       <c r="T4" t="n">
-        <v>174000</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>212000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
       <c r="V4" t="n">
-        <v>703000</v>
+        <v>566000</v>
       </c>
       <c r="W4" t="n">
-        <v>703000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>566000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>154000</v>
+      </c>
       <c r="Y4" t="n">
-        <v>14136000</v>
+        <v>15155000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4969000</v>
+        <v>5143000</v>
       </c>
       <c r="AA4" t="n">
-        <v>697000</v>
+        <v>991000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4272000</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>4152000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-154000</v>
+      </c>
       <c r="AD4" t="n">
-        <v>4559000</v>
+        <v>1850000</v>
       </c>
       <c r="AE4" t="n">
-        <v>3228000</v>
+        <v>3397000</v>
       </c>
       <c r="AF4" t="n">
-        <v>446000</v>
+        <v>348000</v>
       </c>
       <c r="AG4" t="n">
-        <v>885000</v>
+        <v>1502000</v>
       </c>
       <c r="AH4" t="n">
-        <v>26273000</v>
+        <v>29416000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1458000</v>
+        <v>2132000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>221000</v>
+        <v>309000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>167000</v>
+        <v>123000</v>
       </c>
       <c r="AM4" t="n">
-        <v>167000</v>
+        <v>123000</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>1070000</v>
+        <v>1700000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-3818000</v>
+        <v>-3409000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4888000</v>
+        <v>5109000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1070000</v>
+        <v>39000</v>
       </c>
       <c r="AS4" t="n">
-        <v>3004000</v>
+        <v>2932000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1884000</v>
+        <v>2138000</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>24815000</v>
+        <v>27284000</v>
       </c>
       <c r="AW4" t="n">
-        <v>728000</v>
+        <v>505000</v>
       </c>
       <c r="AX4" t="n">
-        <v>837000</v>
+        <v>861000</v>
       </c>
       <c r="AY4" t="n">
-        <v>837000</v>
+        <v>861000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1834000</v>
+        <v>1847000</v>
       </c>
       <c r="BA4" t="n">
-        <v>3210000</v>
+        <v>3931000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-660000</v>
+        <v>-668000</v>
       </c>
       <c r="BC4" t="n">
-        <v>3870000</v>
+        <v>4599000</v>
       </c>
       <c r="BD4" t="n">
-        <v>18206000</v>
+        <v>20140000</v>
       </c>
       <c r="BE4" t="n">
-        <v>3724000</v>
+        <v>3538000</v>
       </c>
       <c r="BF4" t="n">
-        <v>14482000</v>
+        <v>16602000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1509592701</v>
@@ -2041,37 +2043,37 @@
         <v>1509592701</v>
       </c>
       <c r="D5" t="n">
-        <v>6364000</v>
+        <v>4571000</v>
       </c>
       <c r="E5" t="n">
-        <v>10959000</v>
+        <v>15922000</v>
       </c>
       <c r="F5" t="n">
-        <v>15976000</v>
+        <v>19778000</v>
       </c>
       <c r="G5" t="n">
-        <v>9999000</v>
+        <v>15050000</v>
       </c>
       <c r="H5" t="n">
-        <v>10959000</v>
+        <v>15922000</v>
       </c>
       <c r="I5" t="n">
-        <v>1347000</v>
+        <v>715000</v>
       </c>
       <c r="J5" t="n">
-        <v>10959000</v>
+        <v>15922000</v>
       </c>
       <c r="K5" t="n">
-        <v>10959000</v>
+        <v>15922000</v>
       </c>
       <c r="L5" t="n">
-        <v>10959000</v>
+        <v>15922000</v>
       </c>
       <c r="M5" t="n">
-        <v>10959000</v>
+        <v>15922000</v>
       </c>
       <c r="N5" t="n">
-        <v>-167468000</v>
+        <v>-161760000</v>
       </c>
       <c r="O5" t="n">
         <v>153457000</v>
@@ -2083,125 +2085,123 @@
         <v>20128000</v>
       </c>
       <c r="R5" t="n">
-        <v>19889000</v>
+        <v>14087000</v>
       </c>
       <c r="S5" t="n">
-        <v>798000</v>
+        <v>488000</v>
       </c>
       <c r="T5" t="n">
-        <v>257000</v>
+        <v>175000</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="V5" t="n">
-        <v>392000</v>
+        <v>139000</v>
       </c>
       <c r="W5" t="n">
-        <v>392000</v>
+        <v>139000</v>
       </c>
       <c r="X5" t="n">
-        <v>149000</v>
+        <v>154000</v>
       </c>
       <c r="Y5" t="n">
-        <v>19091000</v>
+        <v>13599000</v>
       </c>
       <c r="Z5" t="n">
-        <v>5972000</v>
+        <v>4432000</v>
       </c>
       <c r="AA5" t="n">
-        <v>955000</v>
+        <v>576000</v>
       </c>
       <c r="AB5" t="n">
-        <v>5017000</v>
+        <v>3856000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-149000</v>
+        <v>-154000</v>
       </c>
       <c r="AD5" t="n">
-        <v>8568000</v>
+        <v>4271000</v>
       </c>
       <c r="AE5" t="n">
-        <v>4010000</v>
+        <v>2299000</v>
       </c>
       <c r="AF5" t="n">
-        <v>305000</v>
+        <v>523000</v>
       </c>
       <c r="AG5" t="n">
-        <v>4253000</v>
+        <v>1449000</v>
       </c>
       <c r="AH5" t="n">
-        <v>30848000</v>
+        <v>30009000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1758000</v>
+        <v>1360000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>282000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
+        <v>190000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>135000</v>
+        <v>95000</v>
       </c>
       <c r="AM5" t="n">
-        <v>135000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
+        <v>95000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>1341000</v>
+        <v>1075000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-3646000</v>
+        <v>-3493000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4987000</v>
+        <v>4568000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1341000</v>
+        <v>30000</v>
       </c>
       <c r="AS5" t="n">
-        <v>3080000</v>
+        <v>2996000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1907000</v>
+        <v>1542000</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>29090000</v>
+        <v>28649000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1731000</v>
+        <v>1010000</v>
       </c>
       <c r="AX5" t="n">
-        <v>772000</v>
+        <v>1725000</v>
       </c>
       <c r="AY5" t="n">
-        <v>772000</v>
+        <v>1725000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2477000</v>
+        <v>959000</v>
       </c>
       <c r="BA5" t="n">
-        <v>8006000</v>
+        <v>3901000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-1175000</v>
+        <v>-630000</v>
       </c>
       <c r="BC5" t="n">
-        <v>9181000</v>
+        <v>4531000</v>
       </c>
       <c r="BD5" t="n">
-        <v>16104000</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
+        <v>21054000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5700000</v>
+      </c>
       <c r="BF5" t="n">
-        <v>16104000</v>
+        <v>15354000</v>
       </c>
     </row>
   </sheetData>
@@ -2442,504 +2442,504 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>2009000</v>
+        <v>4238000</v>
       </c>
       <c r="C2" t="n">
-        <v>-295000</v>
+        <v>-1085000</v>
       </c>
       <c r="D2" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-355000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16104000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12249000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>232000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3623000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-888000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-28000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>155000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>155000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-1085000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-82000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>161000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>77000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>77000</v>
+      </c>
+      <c r="W2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>-127000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>15354000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>16602000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-111000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-1137000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1353000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-295000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-295000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-295000</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>-1920000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>367000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-2162000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>77000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-125000</v>
+        <v>-320000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-127000</v>
+        <v>-355000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2136000</v>
+        <v>4593000</v>
       </c>
       <c r="AE2" t="n">
-        <v>5000</v>
+        <v>24000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-49000</v>
+        <v>-74000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-796000</v>
+        <v>1526000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-53000</v>
+        <v>2359000</v>
       </c>
       <c r="AI2" t="n">
-        <v>502000</v>
+        <v>329000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-864000</v>
+        <v>-201000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-5000</v>
+        <v>-4519000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-315000</v>
+        <v>-54000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-171000</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>959000</v>
+        <v>1049000</v>
       </c>
       <c r="AO2" t="n">
-        <v>959000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>28000</v>
-      </c>
+        <v>1049000</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1000</v>
+        <v>-277000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2846000</v>
+        <v>4225000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>2596000</v>
+        <v>4579000</v>
       </c>
       <c r="C3" t="n">
-        <v>-540000</v>
+        <v>-1115000</v>
       </c>
       <c r="D3" t="n">
-        <v>426000</v>
+        <v>446000</v>
       </c>
       <c r="E3" t="n">
-        <v>-307000</v>
+        <v>-164000</v>
       </c>
       <c r="F3" t="n">
-        <v>16602000</v>
+        <v>14482000</v>
       </c>
       <c r="G3" t="n">
-        <v>14482000</v>
+        <v>16104000</v>
       </c>
       <c r="H3" t="n">
-        <v>74000</v>
+        <v>-851000</v>
       </c>
       <c r="I3" t="n">
-        <v>2046000</v>
+        <v>-771000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1179000</v>
+        <v>-1866000</v>
       </c>
       <c r="K3" t="n">
-        <v>-22000</v>
+        <v>-28000</v>
       </c>
       <c r="L3" t="n">
-        <v>-114000</v>
+        <v>-669000</v>
       </c>
       <c r="M3" t="n">
-        <v>-114000</v>
+        <v>-669000</v>
       </c>
       <c r="N3" t="n">
-        <v>-540000</v>
+        <v>-1115000</v>
       </c>
       <c r="O3" t="n">
-        <v>426000</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+        <v>446000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-669000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1115000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>446000</v>
+      </c>
       <c r="S3" t="n">
-        <v>322000</v>
+        <v>-3648000</v>
       </c>
       <c r="T3" t="n">
-        <v>441000</v>
+        <v>240000</v>
       </c>
       <c r="U3" t="n">
-        <v>186000</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>-3724000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-3724000</v>
+      </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>-305000</v>
+        <v>-164000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-307000</v>
+        <v>-164000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2903000</v>
+        <v>4743000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-279000</v>
+        <v>-89000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-90000</v>
+        <v>-71000</v>
       </c>
       <c r="AG3" t="n">
-        <v>480000</v>
+        <v>-725000</v>
       </c>
       <c r="AH3" t="n">
-        <v>617000</v>
+        <v>-3368000</v>
       </c>
       <c r="AI3" t="n">
-        <v>122000</v>
+        <v>1707000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-31000</v>
+        <v>-153000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-745000</v>
+        <v>5015000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-356000</v>
+        <v>-136000</v>
       </c>
       <c r="AM3" t="n">
-        <v>7000</v>
+        <v>-66000</v>
       </c>
       <c r="AN3" t="n">
-        <v>907000</v>
+        <v>1119000</v>
       </c>
       <c r="AO3" t="n">
-        <v>907000</v>
+        <v>1119000</v>
       </c>
       <c r="AP3" t="n">
-        <v>44000</v>
+        <v>-32000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2161000</v>
+        <v>1261000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>4579000</v>
+        <v>2596000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1115000</v>
+        <v>-540000</v>
       </c>
       <c r="D4" t="n">
-        <v>446000</v>
+        <v>426000</v>
       </c>
       <c r="E4" t="n">
-        <v>-164000</v>
+        <v>-307000</v>
       </c>
       <c r="F4" t="n">
+        <v>16602000</v>
+      </c>
+      <c r="G4" t="n">
         <v>14482000</v>
       </c>
-      <c r="G4" t="n">
-        <v>16104000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-851000</v>
+        <v>74000</v>
       </c>
       <c r="I4" t="n">
-        <v>-771000</v>
+        <v>2046000</v>
       </c>
       <c r="J4" t="n">
-        <v>-1866000</v>
+        <v>-1179000</v>
       </c>
       <c r="K4" t="n">
-        <v>-28000</v>
+        <v>-22000</v>
       </c>
       <c r="L4" t="n">
-        <v>-669000</v>
+        <v>-114000</v>
       </c>
       <c r="M4" t="n">
-        <v>-669000</v>
+        <v>-114000</v>
       </c>
       <c r="N4" t="n">
-        <v>-1115000</v>
+        <v>-540000</v>
       </c>
       <c r="O4" t="n">
-        <v>446000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-669000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1115000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>446000</v>
-      </c>
+        <v>426000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-3648000</v>
+        <v>322000</v>
       </c>
       <c r="T4" t="n">
-        <v>240000</v>
+        <v>441000</v>
       </c>
       <c r="U4" t="n">
-        <v>-3724000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-3724000</v>
-      </c>
+        <v>186000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-164000</v>
+        <v>-305000</v>
       </c>
       <c r="AB4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-307000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2903000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-279000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-90000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>480000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>617000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-31000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-745000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-356000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>907000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>907000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>44000</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-164000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>4743000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-89000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-71000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-725000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-3368000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1707000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-153000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>5015000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-136000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-66000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1119000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1119000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-32000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1000</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1261000</v>
+        <v>2161000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>4238000</v>
+        <v>2009000</v>
       </c>
       <c r="C5" t="n">
-        <v>-1085000</v>
+        <v>-295000</v>
       </c>
       <c r="D5" t="n">
-        <v>1240000</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-355000</v>
+        <v>-127000</v>
       </c>
       <c r="F5" t="n">
-        <v>16104000</v>
+        <v>15354000</v>
       </c>
       <c r="G5" t="n">
-        <v>12249000</v>
+        <v>16602000</v>
       </c>
       <c r="H5" t="n">
-        <v>232000</v>
+        <v>-111000</v>
       </c>
       <c r="I5" t="n">
-        <v>3623000</v>
+        <v>-1137000</v>
       </c>
       <c r="J5" t="n">
-        <v>-888000</v>
+        <v>-1353000</v>
       </c>
       <c r="K5" t="n">
-        <v>-28000</v>
+        <v>-3000</v>
       </c>
       <c r="L5" t="n">
-        <v>155000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>155000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-1085000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1240000</v>
-      </c>
+        <v>-295000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-295000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-295000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-82000</v>
+        <v>-1920000</v>
       </c>
       <c r="T5" t="n">
-        <v>161000</v>
+        <v>367000</v>
       </c>
       <c r="U5" t="n">
-        <v>77000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>77000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>77000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>-2162000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-320000</v>
+        <v>-125000</v>
       </c>
       <c r="AB5" t="n">
-        <v>35000</v>
+        <v>2000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-355000</v>
+        <v>-127000</v>
       </c>
       <c r="AD5" t="n">
-        <v>4593000</v>
+        <v>2136000</v>
       </c>
       <c r="AE5" t="n">
-        <v>24000</v>
+        <v>5000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-74000</v>
+        <v>-49000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1526000</v>
+        <v>-796000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2359000</v>
+        <v>-53000</v>
       </c>
       <c r="AI5" t="n">
-        <v>329000</v>
+        <v>502000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-201000</v>
+        <v>-864000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-4519000</v>
+        <v>-5000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-54000</v>
+        <v>-315000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-171000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1049000</v>
+        <v>959000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1049000</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>959000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>28000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-277000</v>
+        <v>-1000</v>
       </c>
       <c r="AS5" t="n">
-        <v>4225000</v>
+        <v>2846000</v>
       </c>
     </row>
   </sheetData>
@@ -3499,187 +3499,187 @@
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Hing Lin  Wong', 'age': 55, 'title': 'CEO, President &amp; Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 8941516, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Arthur Etienne Marie Pruijt', 'age': 58, 'title': 'Senior Vice President of Quality &amp; Compliance', 'yearBorn': 1967, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sau Man  Cheng', 'age': 51, 'title': 'Company Secretary', 'yearBorn': 1974, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Hing Lin  Wong', 'age': 55, 'title': 'CEO, President &amp; Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 8942146, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Arthur Etienne Marie Pruijt', 'age': 58, 'title': 'Senior Vice President of Quality &amp; Compliance', 'yearBorn': 1967, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sau Man  Cheng', 'age': 51, 'title': 'Company Secretary', 'yearBorn': 1974, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3780,25 +3780,25 @@
         <v>0.05</v>
       </c>
       <c r="U2" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="W2" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="X2" t="n">
         <v>0.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="AB2" t="n">
         <v>1482883200</v>
@@ -3810,31 +3810,31 @@
         <v>2.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.411</v>
+        <v>0.422</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.275</v>
+        <v>1.225</v>
       </c>
       <c r="AG2" t="n">
-        <v>234000</v>
+        <v>200000</v>
       </c>
       <c r="AH2" t="n">
-        <v>234000</v>
+        <v>200000</v>
       </c>
       <c r="AI2" t="n">
-        <v>334283</v>
+        <v>285305</v>
       </c>
       <c r="AJ2" t="n">
-        <v>307444</v>
+        <v>196100</v>
       </c>
       <c r="AK2" t="n">
-        <v>307444</v>
+        <v>196100</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.051</v>
+        <v>0.045</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.055</v>
+        <v>0.049</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -3843,16 +3843,16 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>76989224</v>
+        <v>73970040</v>
       </c>
       <c r="AQ2" t="n">
-        <v>75479635</v>
+        <v>73970042</v>
       </c>
       <c r="AR2" t="n">
         <v>0.044</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.126</v>
+        <v>0.102</v>
       </c>
       <c r="AT2" t="n">
         <v>6.933333</v>
@@ -3861,13 +3861,13 @@
         <v>0.033333</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.369118</v>
+        <v>2.2762113</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.05658</v>
+        <v>0.05538</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.06104</v>
+        <v>0.059245</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -3884,7 +3884,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>60823228</v>
+        <v>57804044</v>
       </c>
       <c r="BD2" t="n">
         <v>0.0023700001</v>
@@ -3905,10 +3905,10 @@
         <v>1509592701</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.08620216999999999</v>
+        <v>0.08620825</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5916323999999999</v>
+        <v>0.5683911</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -3940,16 +3940,16 @@
         <v>1502323200</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.872</v>
+        <v>1.779</v>
       </c>
       <c r="BV2" t="n">
-        <v>-105.78</v>
+        <v>-100.529</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0.5575221</v>
+        <v>-0.50505054</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
         <v>0.0046</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -4065,140 +4065,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>-0.0055800006</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-0.09862143499999999</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-0.01004</v>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>DAOHE GLOBAL</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Daohe Global Group Limited</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DH2" t="n">
-        <v>-0.16448231</v>
-      </c>
-      <c r="DI2" t="n">
+        <v>1781677034</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>finmb_7658147</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-2.000004</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
         <v>15</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DT2" t="n">
         <v>15</v>
       </c>
-      <c r="DK2" t="b">
+      <c r="DU2" t="b">
         <v>0</v>
       </c>
-      <c r="DL2" t="b">
+      <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="DW2" t="n">
         <v>1020994200000</v>
       </c>
-      <c r="DN2" t="n">
-        <v>0.0009999983000000001</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>0.05 - 0.051</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DX2" t="n">
+        <v>-0.001000002</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>0.049 - 0.049</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DQ2" t="n">
-        <v>334283</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.0069999993</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.15909089</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>0.044 - 0.126</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.075</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.5952381</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-55.752213</v>
-      </c>
-      <c r="DX2" t="n">
+      <c r="EA2" t="n">
+        <v>285305</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.004999999</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.11363634</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>0.044 - 0.102</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.51960784</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-50.505054</v>
+      </c>
+      <c r="EH2" t="n">
         <v>1742984682</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EI2" t="n">
         <v>1742984682</v>
-      </c>
-      <c r="DZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>1780368800</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>finmb_7658147</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
       </c>
       <c r="EJ2" t="b">
         <v>0</v>
       </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>DAOHE GLOBAL</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>Daohe Global Group Limited</t>
-        </is>
+      <c r="EK2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.006380003</v>
       </c>
       <c r="EM2" t="n">
-        <v>1.9999967</v>
+        <v>-0.115204096</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+        <v>-0.010245003</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.17292602</v>
       </c>
       <c r="EP2" t="inlineStr"/>
     </row>
